--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
+    <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>{{organization.name}}</t>
   </si>
@@ -116,13 +117,202 @@
   </si>
   <si>
     <t>IBAN: {{organization.iban}} | Bank: {{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Available template placeholders</t>
+  </si>
+  <si>
+    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>{{invoice.number}}</t>
+  </si>
+  <si>
+    <t>Invoice number</t>
+  </si>
+  <si>
+    <t>{{invoice.date}}</t>
+  </si>
+  <si>
+    <t>Invoice date</t>
+  </si>
+  <si>
+    <t>{{invoice.dueDate}}</t>
+  </si>
+  <si>
+    <t>Payment due date</t>
+  </si>
+  <si>
+    <t>{{invoice.currency}}</t>
+  </si>
+  <si>
+    <t>Currency code (e.g. EUR)</t>
+  </si>
+  <si>
+    <t>{{invoice.buyerReference}}</t>
+  </si>
+  <si>
+    <t>Buyer reference (e.g. a Leitweg-ID)</t>
+  </si>
+  <si>
+    <t>Seller company name</t>
+  </si>
+  <si>
+    <t>{{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Seller VAT number</t>
+  </si>
+  <si>
+    <t>{{organization.email}}</t>
+  </si>
+  <si>
+    <t>Seller email</t>
+  </si>
+  <si>
+    <t>{{organization.phone}}</t>
+  </si>
+  <si>
+    <t>Seller phone</t>
+  </si>
+  <si>
+    <t>{{organization.website}}</t>
+  </si>
+  <si>
+    <t>Seller website</t>
+  </si>
+  <si>
+    <t>{{organization.street}}</t>
+  </si>
+  <si>
+    <t>Seller street</t>
+  </si>
+  <si>
+    <t>{{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Seller house number</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}}</t>
+  </si>
+  <si>
+    <t>Seller postal code</t>
+  </si>
+  <si>
+    <t>{{organization.city}}</t>
+  </si>
+  <si>
+    <t>Seller city</t>
+  </si>
+  <si>
+    <t>Customer name</t>
+  </si>
+  <si>
+    <t>{{client.vatin}}</t>
+  </si>
+  <si>
+    <t>Customer VAT number</t>
+  </si>
+  <si>
+    <t>{{client.email}}</t>
+  </si>
+  <si>
+    <t>Customer email</t>
+  </si>
+  <si>
+    <t>{{client.phone}}</t>
+  </si>
+  <si>
+    <t>Customer phone</t>
+  </si>
+  <si>
+    <t>{{client.street}}</t>
+  </si>
+  <si>
+    <t>Customer street</t>
+  </si>
+  <si>
+    <t>{{client.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Customer house number</t>
+  </si>
+  <si>
+    <t>{{client.postalCode}}</t>
+  </si>
+  <si>
+    <t>Customer postal code</t>
+  </si>
+  <si>
+    <t>{{client.city}}</t>
+  </si>
+  <si>
+    <t>Customer city</t>
+  </si>
+  <si>
+    <t>Item lines</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in column A of the row to repeat once per line item</t>
+  </si>
+  <si>
+    <t>Line item description</t>
+  </si>
+  <si>
+    <t>Unit price, formatted with currency</t>
+  </si>
+  <si>
+    <t>Tax rate percentage (e.g. 19.5%)</t>
+  </si>
+  <si>
+    <t>Quantity x unit price, formatted with currency</t>
+  </si>
+  <si>
+    <t>Footer</t>
+  </si>
+  <si>
+    <t>Subtotal before tax</t>
+  </si>
+  <si>
+    <t>Total tax</t>
+  </si>
+  <si>
+    <t>Grand total</t>
+  </si>
+  <si>
+    <t>{{invoice.paymentTerms}}</t>
+  </si>
+  <si>
+    <t>Payment terms text</t>
+  </si>
+  <si>
+    <t>{{organization.iban}}</t>
+  </si>
+  <si>
+    <t>Seller IBAN</t>
+  </si>
+  <si>
+    <t>{{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Seller bank name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -145,8 +335,19 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF666666"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,6 +357,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E8F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
@@ -184,6 +390,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,19 +744,20 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -598,4 +817,331 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="14"/>
+    <col customWidth="true" max="2" min="2" width="32"/>
+    <col customWidth="true" max="3" min="3" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="s">
+        <v>95</v>
+      </c>
+      <c r="C41" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A35:C35"/>
+  </mergeCells>
+</worksheet>
 </file>
--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -744,7 +744,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>15</v>
       </c>

--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t>{{organization.name}}</t>
   </si>
@@ -77,24 +77,24 @@
     <t>Line Total</t>
   </si>
   <si>
+    <t>{{lineItems.description}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.quantity}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.unitPrice}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.taxRate}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.lineTotal}}</t>
+  </si>
+  <si>
     <t>{{#lineItems}}</t>
   </si>
   <si>
-    <t>{{lineItems.description}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.quantity}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.unitPrice}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.taxRate}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.lineTotal}}</t>
-  </si>
-  <si>
     <t>Subtotal</t>
   </si>
   <si>
@@ -263,7 +263,7 @@
     <t>Item lines</t>
   </si>
   <si>
-    <t>Marker (not a value) — place alone in column A of the row to repeat once per line item</t>
+    <t>Marker (not a value) — place alone in any one cell of the row to repeat once per line item; that whole cell is blanked in the output</t>
   </si>
   <si>
     <t>Line item description</t>
@@ -294,6 +294,24 @@
   </si>
   <si>
     <t>Payment terms text</t>
+  </si>
+  <si>
+    <t>{{invoice.fiscalStampAmount}}</t>
+  </si>
+  <si>
+    <t>Tunisia timbre fiscal — flat duty, formatted with currency (0 if unused)</t>
+  </si>
+  <si>
+    <t>{{invoice.withholdingTaxRate}}</t>
+  </si>
+  <si>
+    <t>Withholding tax rate percentage, blank if unset</t>
+  </si>
+  <si>
+    <t>{{invoice.withholdingTaxAmount}}</t>
+  </si>
+  <si>
+    <t>Withholding tax amount, formatted with currency, blank if unset</t>
   </si>
   <si>
     <t>{{organization.iban}}</t>
@@ -744,9 +762,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
         <v>16</v>
       </c>
@@ -764,19 +783,19 @@
       <c r="A14" t="s">
         <v>20</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>22</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>23</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>24</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>25</v>
       </c>
     </row>
@@ -815,6 +834,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+  </mergeCells>
 </worksheet>
 </file>
 
@@ -1036,7 +1059,7 @@
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
         <v>82</v>
@@ -1044,7 +1067,7 @@
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
         <v>83</v>
@@ -1052,7 +1075,7 @@
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
         <v>16</v>
@@ -1060,7 +1083,7 @@
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
         <v>84</v>
@@ -1068,7 +1091,7 @@
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
         <v>85</v>
@@ -1076,7 +1099,7 @@
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
         <v>86</v>
@@ -1133,6 +1156,30 @@
       </c>
       <c r="C41" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="s">
+        <v>99</v>
+      </c>
+      <c r="C43" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>{{organization.name}}</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>IBAN: {{organization.iban}} | Bank: {{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Fiscal stamp: {{invoice.fiscalStampAmount}}</t>
+  </si>
+  <si>
+    <t>Withholding tax ({{invoice.withholdingTaxRate}}): {{invoice.withholdingTaxAmount}}</t>
   </si>
   <si>
     <t>Available template placeholders</t>
@@ -833,6 +839,16 @@
         <v>33</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A13:B13"/>
@@ -852,20 +868,20 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>15</v>
@@ -873,47 +889,47 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -921,71 +937,71 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -993,68 +1009,68 @@
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
@@ -1062,7 +1078,7 @@
         <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
@@ -1070,7 +1086,7 @@
         <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
@@ -1086,7 +1102,7 @@
         <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33">
@@ -1094,7 +1110,7 @@
         <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34">
@@ -1102,12 +1118,12 @@
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36">
@@ -1115,7 +1131,7 @@
         <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37">
@@ -1123,7 +1139,7 @@
         <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38">
@@ -1131,55 +1147,55 @@
         <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -694,6 +694,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -854,6 +857,7 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
   </mergeCells>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 

--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -10,6 +10,9 @@
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Invoice'!$1:$13</definedName>
+  </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
@@ -858,6 +861,10 @@
     <mergeCell ref="A14:B14"/>
   </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
+    <evenFooter>&amp;CPage &amp;P of &amp;N</evenFooter>
+  </headerFooter>
 </worksheet>
 </file>
 

--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>{{organization.name}}</t>
   </si>
@@ -333,6 +333,27 @@
   </si>
   <si>
     <t>Seller bank name</t>
+  </si>
+  <si>
+    <t>Export info</t>
+  </si>
+  <si>
+    <t>{{export.generatedDate}}</t>
+  </si>
+  <si>
+    <t>Date this file was exported (not the invoice's own date), in the organization's date format</t>
+  </si>
+  <si>
+    <t>{{export.generatedTime}}</t>
+  </si>
+  <si>
+    <t>Time this file was exported, 24-hour HH:MM, server time</t>
+  </si>
+  <si>
+    <t>&amp;P (page number) / &amp;N (total pages)</t>
+  </si>
+  <si>
+    <t>Native Excel/LibreOffice codes, not a {{}} placeholder — only work inside this sheet's own Page Layout ▸ Header/Footer, never in a regular cell, since the page count isn't known until export. The default footer already shows "Page &amp;P of &amp;N" on every page; edit it in Excel/LibreOffice's own header/footer editor to move or restyle it</t>
   </si>
 </sst>
 </file>
@@ -1209,12 +1230,42 @@
         <v>104</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C48" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A45:C45"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>{{organization.name}}</t>
   </si>
@@ -125,7 +125,7 @@
     <t>Fiscal stamp: {{invoice.fiscalStampAmount}}</t>
   </si>
   <si>
-    <t>Withholding tax ({{invoice.withholdingTaxRate}}): {{invoice.withholdingTaxAmount}}</t>
+    <t>{{invoice.withholdingTaxLine}}</t>
   </si>
   <si>
     <t>Available template placeholders</t>
@@ -311,16 +311,7 @@
     <t>Tunisia timbre fiscal — flat duty, formatted with currency (0 if unused)</t>
   </si>
   <si>
-    <t>{{invoice.withholdingTaxRate}}</t>
-  </si>
-  <si>
-    <t>Withholding tax rate percentage, blank if unset</t>
-  </si>
-  <si>
-    <t>{{invoice.withholdingTaxAmount}}</t>
-  </si>
-  <si>
-    <t>Withholding tax amount, formatted with currency, blank if unset</t>
+    <t>Full "Withholding tax (12%): 40.00 EUR" line, entirely blank (not just the rate/amount) if unset</t>
   </si>
   <si>
     <t>{{organization.iban}}</t>
@@ -1200,63 +1191,55 @@
     </row>
     <row r="41">
       <c r="B41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" t="s">
         <v>97</v>
-      </c>
-      <c r="C41" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" t="s">
         <v>99</v>
-      </c>
-      <c r="C42" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" t="s">
         <v>101</v>
       </c>
-      <c r="C43" t="s">
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" t="s">
+    <row r="45">
+      <c r="B45" t="s">
         <v>103</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="s">
+        <v>105</v>
+      </c>
+      <c r="C46" t="s">
         <v>106</v>
-      </c>
-      <c r="C46" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C47" t="s">
         <v>108</v>
-      </c>
-      <c r="C47" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="s">
-        <v>110</v>
-      </c>
-      <c r="C48" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1265,7 +1248,7 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A44:C44"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -807,16 +807,16 @@
       <c r="A14" t="s">
         <v>20</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G14" t="s">

--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>{{organization.name}}</t>
   </si>
@@ -65,6 +65,9 @@
     <t>VAT: {{client.vatin}}</t>
   </si>
   <si>
+    <t>Product</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
@@ -80,6 +83,9 @@
     <t>Line Total</t>
   </si>
   <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
     <t>{{lineItems.description}}</t>
   </si>
   <si>
@@ -273,6 +279,9 @@
   </si>
   <si>
     <t>Marker (not a value) — place alone in any one cell of the row to repeat once per line item; that whole cell is blanked in the output</t>
+  </si>
+  <si>
+    <t>Linked product's SKU, blank on a free-text line or an unset SKU</t>
   </si>
   <si>
     <t>Line item description</t>
@@ -715,7 +724,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="2" min="1" width="28"/>
+    <col customWidth="true" max="1" min="1" width="16"/>
+    <col customWidth="true" max="2" min="2" width="40"/>
     <col customWidth="true" max="5" min="3" width="14"/>
     <col customWidth="true" max="6" min="6" width="16"/>
   </cols>
@@ -789,89 +799,90 @@
       <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="C13" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
       <c r="E17" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="E18" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="E19" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-  </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
@@ -891,68 +902,68 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -960,71 +971,71 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -1032,129 +1043,129 @@
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="s">
-        <v>89</v>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" t="s">
-        <v>90</v>
+      <c r="A36" s="7" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="37">
@@ -1162,7 +1173,7 @@
         <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38">
@@ -1170,76 +1181,84 @@
         <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="s">
-        <v>102</v>
+      <c r="B44" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="s">
-        <v>103</v>
-      </c>
-      <c r="C45" t="s">
-        <v>104</v>
+      <c r="A45" s="7" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C47" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="s">
+        <v>110</v>
+      </c>
+      <c r="C48" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1247,8 +1266,8 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A45:C45"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -724,7 +724,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="16"/>
+    <col customWidth="true" max="1" min="1" width="22"/>
     <col customWidth="true" max="2" min="2" width="40"/>
     <col customWidth="true" max="5" min="3" width="14"/>
     <col customWidth="true" max="6" min="6" width="16"/>
